--- a/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/no_clasificados.xlsx
+++ b/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/no_clasificados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>fecha</t>
   </si>
@@ -58,42 +58,9 @@
     <t>2026-02-10</t>
   </si>
   <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2026-03-14</t>
   </si>
   <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
     <t>2026-02-22</t>
   </si>
   <si>
@@ -103,18 +70,12 @@
     <t>Banca Corporativa</t>
   </si>
   <si>
+    <t>Seguros</t>
+  </si>
+  <si>
     <t>Tarjetas</t>
   </si>
   <si>
-    <t>Corporativo</t>
-  </si>
-  <si>
-    <t>Inversiones</t>
-  </si>
-  <si>
-    <t>Seguros</t>
-  </si>
-  <si>
     <t>Provisión</t>
   </si>
   <si>
@@ -142,18 +103,9 @@
     <t>Sofía Hernández</t>
   </si>
   <si>
-    <t>Javier Morales</t>
-  </si>
-  <si>
     <t>María Sánchez</t>
   </si>
   <si>
-    <t>Daniela Vargas</t>
-  </si>
-  <si>
-    <t>Andrés García</t>
-  </si>
-  <si>
     <t>Ricardo Torres</t>
   </si>
   <si>
@@ -161,21 +113,6 @@
   </si>
   <si>
     <t>banca_corporativa.xlsx</t>
-  </si>
-  <si>
-    <t>cumplimiento.xlsx</t>
-  </si>
-  <si>
-    <t>inversiones.xlsx</t>
-  </si>
-  <si>
-    <t>proveedor_servicios.xlsx</t>
-  </si>
-  <si>
-    <t>proveedor_ti.xlsx</t>
-  </si>
-  <si>
-    <t>riesgos.xlsx</t>
   </si>
   <si>
     <t>seguros.xlsx</t>
@@ -516,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -556,7 +493,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>6120</v>
@@ -565,19 +502,19 @@
         <v>4388550.31</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -585,7 +522,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>5210</v>
@@ -594,19 +531,19 @@
         <v>2078014.58</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -614,7 +551,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>6120</v>
@@ -623,19 +560,19 @@
         <v>1954368.85</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -643,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>5110</v>
@@ -652,19 +589,19 @@
         <v>3193953.22</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -672,28 +609,28 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>6210</v>
+      </c>
+      <c r="E6">
+        <v>2668885.34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="D6">
-        <v>6310</v>
-      </c>
-      <c r="E6">
-        <v>366890.52</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>49</v>
-      </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -701,405 +638,28 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>4120</v>
+      </c>
+      <c r="E7">
+        <v>825079.36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
         <v>30</v>
       </c>
-      <c r="D7">
-        <v>5210</v>
-      </c>
-      <c r="E7">
-        <v>1040201.25</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
       <c r="J7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>5610</v>
-      </c>
-      <c r="E8">
-        <v>4034702.91</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
-        <v>6410</v>
-      </c>
-      <c r="E9">
-        <v>4285384.77</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>5510</v>
-      </c>
-      <c r="E10">
-        <v>2457335.58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>5320</v>
-      </c>
-      <c r="E11">
-        <v>2501177.25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12">
-        <v>5320</v>
-      </c>
-      <c r="E12">
-        <v>3200526.67</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13">
-        <v>5310</v>
-      </c>
-      <c r="E13">
-        <v>3698863.1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14">
-        <v>6120</v>
-      </c>
-      <c r="E14">
-        <v>4386320.25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>6120</v>
-      </c>
-      <c r="E15">
-        <v>4759236.18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16">
-        <v>6310</v>
-      </c>
-      <c r="E16">
-        <v>3335179.82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17">
-        <v>6410</v>
-      </c>
-      <c r="E17">
-        <v>1269845.13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18">
-        <v>6120</v>
-      </c>
-      <c r="E18">
-        <v>219704.38</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19">
-        <v>6210</v>
-      </c>
-      <c r="E19">
-        <v>2668885.34</v>
-      </c>
-      <c r="F19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20">
-        <v>4120</v>
-      </c>
-      <c r="E20">
-        <v>825079.36</v>
-      </c>
-      <c r="F20" t="s">
         <v>35</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
